--- a/tests/uat_testing/handuflow_dir_full_load/master_specs.xlsx
+++ b/tests/uat_testing/handuflow_dir_full_load/master_specs.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="0"/>
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="master_specs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>feed_id</t>
   </si>
@@ -85,7 +85,7 @@
     <t>LANGUAGE</t>
   </si>
   <si>
-    <t>BRONZE_TO_SILVER</t>
+    <t>WITHIN_UNITY_CATALOG</t>
   </si>
   <si>
     <t>BRONZE</t>
@@ -158,6 +158,9 @@
   <si>
     <t>t_iso_language_codes</t>
   </si>
+  <si>
+    <t>t_uid_1_YGCLD_FULL_LOAD_iso_language_codes</t>
+  </si>
 </sst>
 </file>
 
@@ -168,10 +171,10 @@
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.000000"/>
-      <name val="Arial"/>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -182,7 +185,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -190,36 +193,36 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
-      <protection hidden="0" locked="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment wrapText="1"/>
-      <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -229,32 +232,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="master_specs" ref="A1:R2" headerRowCount="1" totalsRowCount="0">
-  <autoFilter ref="A1:R2"/>
-  <tableColumns count="18">
-    <tableColumn id="1" name="feed_id"/>
-    <tableColumn id="2" name="system_name"/>
-    <tableColumn id="3" name="subsystem_name"/>
-    <tableColumn id="4" name="category"/>
-    <tableColumn id="5" name="sub_category"/>
-    <tableColumn id="6" name="data_flow_direction"/>
-    <tableColumn id="7" name="residing_layer"/>
-    <tableColumn id="8" name="feed_name"/>
-    <tableColumn id="9" name="feed_type"/>
-    <tableColumn id="10" name="feed_specs"/>
-    <tableColumn id="11" name="load_type"/>
-    <tableColumn id="12" name="target_unity_catalog"/>
-    <tableColumn id="13" name="target_schema_name"/>
-    <tableColumn id="14" name="target_table_name"/>
-    <tableColumn id="15" name="suggested_feed_name"/>
-    <tableColumn id="16" name="parallelism_group_number"/>
-    <tableColumn id="17" name="parent_feed_id"/>
-    <tableColumn id="18" name="is_active"/>
-  </tableColumns>
-</table>
 </file>
 
 <file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
@@ -541,49 +518,49 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface="Arial"/>
         <a:cs typeface="Arial"/>
       </a:majorFont>
@@ -593,7 +570,7 @@
         <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -602,106 +579,156 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -712,33 +739,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" style="0" width="10.140000000000001"/>
-    <col customWidth="1" min="2" max="2" style="0" width="15.720000000000001"/>
-    <col customWidth="1" min="3" max="3" style="0" width="18.859999999999999"/>
-    <col customWidth="1" min="4" max="4" style="0" width="10.859999999999999"/>
-    <col customWidth="1" min="5" max="5" style="0" width="15"/>
-    <col customWidth="1" min="6" max="6" style="0" width="21.43"/>
-    <col customWidth="1" min="7" max="7" style="0" width="16"/>
-    <col customWidth="1" min="8" max="8" style="0" width="23.43"/>
-    <col customWidth="1" min="9" max="9" style="0" width="15.720000000000001"/>
-    <col customWidth="1" min="10" max="10" style="0" width="109.69"/>
-    <col customWidth="1" min="11" max="11" style="0" width="21.140000000000001"/>
-    <col customWidth="1" min="12" max="12" style="0" width="21.710000000000001"/>
-    <col customWidth="1" min="13" max="13" style="0" width="22.57"/>
-    <col customWidth="1" min="14" max="14" style="0" width="42.289999999999999"/>
-    <col customWidth="1" min="15" max="15" style="0" width="54"/>
-    <col customWidth="1" min="16" max="16" style="0" width="27.859999999999999"/>
-    <col customWidth="1" min="17" max="17" style="0" width="17.140000000000001"/>
-    <col customWidth="1" min="18" max="18" style="0" width="11"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -794,52 +801,51 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="83.650000000000006" customHeight="1">
+    <row r="2" ht="409.5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" t="s">
         <v>30</v>
       </c>
-      <c r="O2" t="str">
-        <f>_xlfn.CONCAT("t_uid_",A2,"_",LEFT(B2, 1), LEFT(C2, 1), LEFT(D2, 1), LEFT(E2, 1), LEFT(I2, 1), "_", K2,"_",H2)</f>
-        <v>t_uid_1_YGCLD_FULL_LOAD_iso_language_codes</v>
+      <c r="O2" t="s">
+        <v>31</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -847,213 +853,14 @@
       <c r="Q2">
         <v>0</v>
       </c>
-      <c r="R2" s="1" t="b">
-        <f>TRUE()</f>
+      <c r="R2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="1048576" ht="12.800000000000001"/>
   </sheetData>
-  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="2" aboveAverage="0" rank="0" text="" id="{1AE6B0EB-D44D-4B57-B765-EAF886BD4194}">
-            <xm:f>LEN(TRIM(#REF!))=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="2"/>
-                  <bgColor indexed="2"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A2:R2</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="" id="{1FFF8B09-1C83-43D4-8254-35C0D7AF04D9}">
-            <xm:f>0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="2"/>
-                  <bgColor indexed="2"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A2</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="4" aboveAverage="0" rank="0" text="" id="{6F618263-BE2D-4B1E-B11D-08642D4CD713}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="2"/>
-                  <bgColor indexed="2"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A2</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="5" aboveAverage="0" rank="0" text="" id="{2FCA703F-E34D-46AD-81EE-01ED023E49E5}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="2"/>
-                  <bgColor indexed="2"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>H2</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="6" aboveAverage="0" rank="0" text="" id="{D4FD27C0-A6A0-44BE-AF45-504CCC1FFA3E}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="2"/>
-                  <bgColor indexed="2"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>N2</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="13" disablePrompts="0">
-        <x14:dataValidation xr:uid="{76DE4531-731E-455F-932B-0E3A5420A889}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"YALS_WORLD"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>B2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{7FC6696D-8093-404B-AC13-83231154A552}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"DATA_ENRICHMENT,GENERIC"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>C2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{4B0115E5-28AC-45DA-84C4-9BCDAAB92D24}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"CODES,RELIGION"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>D2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{09A1E177-2FCB-4623-9D66-CC787B26B7A0}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"COUNTRY,LANGUAGE,HINDUISM,ISLAM,CHRISTIANITY"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{13C2145E-457A-4780-9BBF-F8D114C23818}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"DELTA_TABLE,JSON,CSV,PARQUET,XLSX,XML"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>I2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{F0D89E69-3951-41CD-A53A-EE84B7F31E1C}" type="custom" allowBlank="0" error="Please read the feed name rules by clicking on the feed_name data cell. Non-Compliance to feed name rules is strictly prohibited. Even if excel validation is successful, SDMF may not process feeds if rules are invalidated." errorStyle="stop" errorTitle="INVALID TARGET TABLE NAME" imeMode="noControl" operator="between" prompt="1.No leading or trailing spaces&#10;2.No spaces inside the text&#10;3.All lowercase letters&#10;4.Does not start with a number&#10;5.Length is at least 3 characters&#10;6.Length is no more than 50 characters&#10;7.Text must start with &quot;t_&quot;&#10;DO NOT INCLUDE SPECIAL CHARACTERS" promptTitle="Target Table Name Rules" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>AND(#REF!&lt;&gt;"",#REF!=TRIM(#REF!),ISERROR(SEARCH(" ",#REF!)),#REF!=LOWER(#REF!),NOT(ISNUMBER(--LEFT(#REF!,1))),LEN(#REF!)&gt;=3,LEN(#REF!)&lt;=50,LEFT(#REF!,2)="t_")</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>N2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{EC7E19DA-A587-4F79-AE4D-DC27354F426E}" type="none" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>0</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>H2 J2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{CDEA3CA5-8EE3-497C-98EE-F378B929D27E}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"EXTRACTION,SOURCE_TO_BRONZE,BRONZE_TO_SILVER,SILVER_TO_GOLD"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>F2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{600786F1-4325-4563-BAAF-CC6EB8564178}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>R2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{489D70D5-BF34-4BDE-BC2D-645FA56721EE}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"testing,yalsworld_datawarehouse"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>L2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{7D58F52F-8B39-415F-8EB4-1EF63DD52344}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"bronze,silver,gold"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>M2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{AC150514-F214-4AE5-9CB2-0F51558EC26E}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"FULL_LOAD,APPEND_LOAD,INCREMENTAL_CDC,SCD_TYPE_2,API_EXTRACTOR,STORAGE_FETCH"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>K2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{D55DEF87-BFB8-4813-BE48-72786AF45A32}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>"SOURCE,BRONZE,SILVER,GOLD"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/tests/uat_testing/handuflow_dir_full_load/master_specs.xlsx
+++ b/tests/uat_testing/handuflow_dir_full_load/master_specs.xlsx
@@ -744,6 +744,9 @@
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="10" max="10" width="31.28125"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
